--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:20</t>
+    <t xml:space="preserve">2026-09-29 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:11</t>
+    <t xml:space="preserve">2026-09-29 18:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,10 +490,10 @@
         <v>8.04</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45.52</v>
+        <v>45.53</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>37.49</v>
+        <v>37.48</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
         <v>7.41</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>52.64</v>
+        <v>52.63</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>45.23</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:46</t>
+    <t xml:space="preserve">2026-10-05 04:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>45.53</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>37.48</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
         <v>7.41</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>52.63</v>
+        <v>52.64</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>45.23</v>
@@ -518,7 +518,7 @@
         <v>0.38</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>37.6</v>
+        <v>37.61</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>37.23</v>
